--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:44</t>
+    <t xml:space="preserve">2026-09-09 22:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:32</t>
+    <t xml:space="preserve">2026-09-12 19:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:48</t>
+    <t xml:space="preserve">2026-09-24 00:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:26</t>
+    <t xml:space="preserve">2026-09-27 23:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -505,7 +505,7 @@
         <v>2019</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7.62</v>
+        <v>76.24</v>
       </c>
     </row>
     <row r="3">
@@ -522,7 +522,7 @@
         <v>2019</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>5.7</v>
+        <v>56.99</v>
       </c>
     </row>
     <row r="4">
@@ -539,7 +539,7 @@
         <v>2019</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.88</v>
+        <v>8.76</v>
       </c>
     </row>
     <row r="5">
@@ -573,7 +573,7 @@
         <v>2019</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.14</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="7">
@@ -590,7 +590,7 @@
         <v>2019</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.18</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="8">
@@ -607,7 +607,7 @@
         <v>2019</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.25</v>
+        <v>-2.53</v>
       </c>
     </row>
     <row r="9">
@@ -624,7 +624,7 @@
         <v>2019</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-1.33</v>
+        <v>-13.33</v>
       </c>
     </row>
     <row r="10">
@@ -641,7 +641,7 @@
         <v>2019</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-1.69</v>
+        <v>-16.88</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:09</t>
+    <t xml:space="preserve">2026-10-01 20:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:55</t>
+    <t xml:space="preserve">2026-10-02 13:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:24</t>
+    <t xml:space="preserve">2026-10-05 08:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
